--- a/config.xlsx
+++ b/config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\OneDrive\Escritorio\bio-quim\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\OneDrive\Escritorio\bio-quim\bio-quim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B127BBAF-C5F3-4AF8-81D3-E7A71B925A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D30C761A-AD2A-4AE9-89BF-8EF1D248C6D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Productos" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,9 @@
     <sheet name="configuracion" sheetId="3" r:id="rId4"/>
     <sheet name="hero" sheetId="4" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Productos!$A$1:$K$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -744,7 +747,6 @@
         <v>53</v>
       </c>
       <c r="D3">
-        <f>1250*5</f>
         <v>6250</v>
       </c>
       <c r="E3" t="s">
@@ -783,7 +785,6 @@
         <v>53</v>
       </c>
       <c r="D5">
-        <f>1250*5</f>
         <v>6250</v>
       </c>
       <c r="E5" t="s">
@@ -1002,8 +1003,7 @@
         <v>50</v>
       </c>
       <c r="D17">
-        <f>+D6+5</f>
-        <v>905</v>
+        <v>4500</v>
       </c>
       <c r="E17" t="s">
         <v>67</v>
@@ -1020,8 +1020,7 @@
         <v>50</v>
       </c>
       <c r="D18">
-        <f t="shared" ref="D18:D27" si="0">+D7+5</f>
-        <v>1255</v>
+        <v>6250</v>
       </c>
       <c r="E18" t="s">
         <v>67</v>
@@ -1038,8 +1037,7 @@
         <v>51</v>
       </c>
       <c r="D19">
-        <f t="shared" si="0"/>
-        <v>405</v>
+        <v>2000</v>
       </c>
       <c r="E19" t="s">
         <v>67</v>
@@ -1056,8 +1054,7 @@
         <v>51</v>
       </c>
       <c r="D20">
-        <f t="shared" si="0"/>
-        <v>1105</v>
+        <v>5500</v>
       </c>
       <c r="E20" t="s">
         <v>67</v>
@@ -1074,8 +1071,7 @@
         <v>48</v>
       </c>
       <c r="D21">
-        <f t="shared" si="0"/>
-        <v>1105</v>
+        <v>5500</v>
       </c>
       <c r="E21" t="s">
         <v>67</v>
@@ -1092,8 +1088,7 @@
         <v>49</v>
       </c>
       <c r="D22">
-        <f t="shared" si="0"/>
-        <v>505</v>
+        <v>2500</v>
       </c>
       <c r="E22" t="s">
         <v>67</v>
@@ -1110,8 +1105,7 @@
         <v>51</v>
       </c>
       <c r="D23">
-        <f t="shared" si="0"/>
-        <v>905</v>
+        <v>4500</v>
       </c>
       <c r="E23" t="s">
         <v>67</v>
@@ -1128,8 +1122,7 @@
         <v>73</v>
       </c>
       <c r="D24">
-        <f t="shared" si="0"/>
-        <v>1855</v>
+        <v>9250</v>
       </c>
       <c r="E24" t="s">
         <v>67</v>
@@ -1146,8 +1139,7 @@
         <v>53</v>
       </c>
       <c r="D25">
-        <f t="shared" si="0"/>
-        <v>1255</v>
+        <v>6250</v>
       </c>
       <c r="E25" t="s">
         <v>67</v>
@@ -1164,8 +1156,7 @@
         <v>54</v>
       </c>
       <c r="D26">
-        <f t="shared" si="0"/>
-        <v>1505</v>
+        <v>7500</v>
       </c>
       <c r="E26" t="s">
         <v>67</v>
@@ -1182,14 +1173,14 @@
         <v>55</v>
       </c>
       <c r="D27">
-        <f t="shared" si="0"/>
-        <v>9505</v>
+        <v>47500</v>
       </c>
       <c r="E27" t="s">
         <v>67</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/config.xlsx
+++ b/config.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\OneDrive\Escritorio\bio-quim\bio-quim\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\OneDrive\Escritorio\bio-quim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D30C761A-AD2A-4AE9-89BF-8EF1D248C6D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BDB10C8-B1F0-4AAE-B09A-9D0B88D2065A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,9 +19,6 @@
     <sheet name="configuracion" sheetId="3" r:id="rId4"/>
     <sheet name="hero" sheetId="4" r:id="rId5"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Productos!$A$1:$K$1</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -747,6 +744,7 @@
         <v>53</v>
       </c>
       <c r="D3">
+        <f>1250*5</f>
         <v>6250</v>
       </c>
       <c r="E3" t="s">
@@ -785,6 +783,7 @@
         <v>53</v>
       </c>
       <c r="D5">
+        <f>1250*5</f>
         <v>6250</v>
       </c>
       <c r="E5" t="s">
@@ -804,7 +803,7 @@
         <v>50</v>
       </c>
       <c r="D6">
-        <v>900</v>
+        <v>960</v>
       </c>
       <c r="E6" t="s">
         <v>64</v>
@@ -840,7 +839,7 @@
         <v>51</v>
       </c>
       <c r="D8">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E8" t="s">
         <v>64</v>
@@ -876,7 +875,7 @@
         <v>48</v>
       </c>
       <c r="D10">
-        <v>1100</v>
+        <v>1200</v>
       </c>
       <c r="E10" t="s">
         <v>64</v>
@@ -894,7 +893,7 @@
         <v>49</v>
       </c>
       <c r="D11">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="E11" t="s">
         <v>64</v>
@@ -913,7 +912,7 @@
         <v>51</v>
       </c>
       <c r="D12">
-        <v>900</v>
+        <v>1500</v>
       </c>
       <c r="E12" t="s">
         <v>64</v>
@@ -949,7 +948,7 @@
         <v>53</v>
       </c>
       <c r="D14">
-        <v>1250</v>
+        <v>1500</v>
       </c>
       <c r="E14" t="s">
         <v>64</v>
@@ -967,7 +966,7 @@
         <v>54</v>
       </c>
       <c r="D15">
-        <v>1500</v>
+        <v>1600</v>
       </c>
       <c r="E15" t="s">
         <v>64</v>
@@ -985,7 +984,7 @@
         <v>55</v>
       </c>
       <c r="D16">
-        <v>9500</v>
+        <v>1900</v>
       </c>
       <c r="E16" t="s">
         <v>64</v>
@@ -1003,7 +1002,8 @@
         <v>50</v>
       </c>
       <c r="D17">
-        <v>4500</v>
+        <f>+D6*5</f>
+        <v>4800</v>
       </c>
       <c r="E17" t="s">
         <v>67</v>
@@ -1020,6 +1020,7 @@
         <v>50</v>
       </c>
       <c r="D18">
+        <f t="shared" ref="D18:D27" si="0">+D7*5</f>
         <v>6250</v>
       </c>
       <c r="E18" t="s">
@@ -1037,7 +1038,8 @@
         <v>51</v>
       </c>
       <c r="D19">
-        <v>2000</v>
+        <f t="shared" si="0"/>
+        <v>3000</v>
       </c>
       <c r="E19" t="s">
         <v>67</v>
@@ -1054,6 +1056,7 @@
         <v>51</v>
       </c>
       <c r="D20">
+        <f t="shared" si="0"/>
         <v>5500</v>
       </c>
       <c r="E20" t="s">
@@ -1071,7 +1074,8 @@
         <v>48</v>
       </c>
       <c r="D21">
-        <v>5500</v>
+        <f t="shared" si="0"/>
+        <v>6000</v>
       </c>
       <c r="E21" t="s">
         <v>67</v>
@@ -1088,7 +1092,8 @@
         <v>49</v>
       </c>
       <c r="D22">
-        <v>2500</v>
+        <f t="shared" si="0"/>
+        <v>3000</v>
       </c>
       <c r="E22" t="s">
         <v>67</v>
@@ -1105,7 +1110,8 @@
         <v>51</v>
       </c>
       <c r="D23">
-        <v>4500</v>
+        <f t="shared" si="0"/>
+        <v>7500</v>
       </c>
       <c r="E23" t="s">
         <v>67</v>
@@ -1122,6 +1128,7 @@
         <v>73</v>
       </c>
       <c r="D24">
+        <f t="shared" si="0"/>
         <v>9250</v>
       </c>
       <c r="E24" t="s">
@@ -1139,7 +1146,8 @@
         <v>53</v>
       </c>
       <c r="D25">
-        <v>6250</v>
+        <f t="shared" si="0"/>
+        <v>7500</v>
       </c>
       <c r="E25" t="s">
         <v>67</v>
@@ -1156,7 +1164,8 @@
         <v>54</v>
       </c>
       <c r="D26">
-        <v>7500</v>
+        <f t="shared" si="0"/>
+        <v>8000</v>
       </c>
       <c r="E26" t="s">
         <v>67</v>
@@ -1173,14 +1182,14 @@
         <v>55</v>
       </c>
       <c r="D27">
-        <v>47500</v>
+        <f t="shared" si="0"/>
+        <v>9500</v>
       </c>
       <c r="E27" t="s">
         <v>67</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/config.xlsx
+++ b/config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kevin\OneDrive\Escritorio\bio-quim\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BDB10C8-B1F0-4AAE-B09A-9D0B88D2065A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{164082F8-ABBD-46E6-8680-4100532FE312}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -984,7 +984,7 @@
         <v>55</v>
       </c>
       <c r="D16">
-        <v>1900</v>
+        <v>9500</v>
       </c>
       <c r="E16" t="s">
         <v>64</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="D27">
         <f t="shared" si="0"/>
-        <v>9500</v>
+        <v>47500</v>
       </c>
       <c r="E27" t="s">
         <v>67</v>
